--- a/uploads/Reporte_Actividades_Materno.xlsx
+++ b/uploads/Reporte_Actividades_Materno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jhon\Esni app\materno\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C428C5B8-D024-48E5-A7ED-98EA3C25FFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A3D0D8-0789-4F95-A19B-2BC30536DDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1395,161 +1395,161 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1839,50 +1839,50 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="86"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="86"/>
-      <c r="T5" s="86"/>
-      <c r="U5" s="86"/>
-      <c r="V5" s="86"/>
-      <c r="W5" s="86"/>
-      <c r="X5" s="86"/>
-      <c r="Y5" s="86"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="38"/>
+      <c r="X5" s="38"/>
+      <c r="Y5" s="38"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
     </row>
     <row r="8" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="M8" s="2"/>
@@ -1910,84 +1910,84 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="51" t="s">
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="64"/>
-      <c r="J13" s="51" t="s">
+      <c r="I13" s="46"/>
+      <c r="J13" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="K13" s="64"/>
-      <c r="L13" s="51" t="s">
+      <c r="K13" s="46"/>
+      <c r="L13" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="64"/>
-      <c r="N13" s="41" t="s">
+      <c r="M13" s="46"/>
+      <c r="N13" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="O13" s="87"/>
-      <c r="P13" s="88"/>
-      <c r="Q13" s="89" t="s">
+      <c r="O13" s="50"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="R13" s="74"/>
-      <c r="S13" s="89" t="s">
+      <c r="R13" s="54"/>
+      <c r="S13" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="T13" s="64"/>
-      <c r="U13" s="53" t="s">
+      <c r="T13" s="46"/>
+      <c r="U13" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="V13" s="65" t="s">
+      <c r="V13" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="W13" s="75"/>
-      <c r="X13" s="75"/>
-      <c r="Y13" s="75"/>
-      <c r="Z13" s="66"/>
-      <c r="AA13" s="68" t="s">
+      <c r="W13" s="52"/>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="52"/>
+      <c r="Z13" s="48"/>
+      <c r="AA13" s="56" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="84"/>
-      <c r="B14" s="56" t="s">
+      <c r="A14" s="40"/>
+      <c r="B14" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="63" t="s">
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="65"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="66"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="65"/>
-      <c r="T14" s="66"/>
-      <c r="U14" s="53"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="48"/>
+      <c r="U14" s="55"/>
       <c r="V14" s="7" t="s">
         <v>18</v>
       </c>
@@ -2003,10 +2003,10 @@
       <c r="Z14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AA14" s="82"/>
+      <c r="AA14" s="57"/>
     </row>
     <row r="15" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="85"/>
+      <c r="A15" s="41"/>
       <c r="B15" s="6" t="s">
         <v>23</v>
       </c>
@@ -2019,8 +2019,8 @@
       <c r="E15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
       <c r="H15" s="6" t="s">
         <v>27</v>
       </c>
@@ -2060,7 +2060,7 @@
       <c r="T15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="U15" s="53"/>
+      <c r="U15" s="55"/>
       <c r="V15" s="6" t="s">
         <v>36</v>
       </c>
@@ -2084,10 +2084,7 @@
       <c r="A16" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="14">
-        <f t="shared" ref="B16:B20" si="0">SUM(C16:E16)</f>
-        <v>0</v>
-      </c>
+      <c r="B16" s="14"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
@@ -2118,10 +2115,7 @@
       <c r="A17" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="B17" s="14"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -2152,10 +2146,7 @@
       <c r="A18" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="B18" s="14"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
@@ -2186,10 +2177,7 @@
       <c r="A19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="B19" s="14"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
@@ -2220,10 +2208,7 @@
       <c r="A20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
@@ -2251,69 +2236,69 @@
       <c r="AA20" s="14"/>
     </row>
     <row r="22" spans="1:27" s="15" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="51" t="s">
+      <c r="C22" s="46"/>
+      <c r="D22" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="64"/>
-      <c r="F22" s="51" t="s">
+      <c r="E22" s="46"/>
+      <c r="F22" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="54"/>
-      <c r="I22" s="48" t="s">
+      <c r="G22" s="62"/>
+      <c r="I22" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="J22" s="60" t="s">
+      <c r="J22" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="61"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="61"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="73"/>
-      <c r="Q22" s="51" t="s">
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="R22" s="74"/>
-      <c r="S22" s="74"/>
-      <c r="T22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="62"/>
     </row>
     <row r="23" spans="1:27" s="15" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="67"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="56" t="s">
+      <c r="A23" s="40"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="63"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="56" t="s">
+      <c r="K23" s="59"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="O23" s="58"/>
+      <c r="O23" s="60"/>
       <c r="P23" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="75"/>
-      <c r="S23" s="75"/>
-      <c r="T23" s="67"/>
+      <c r="Q23" s="47"/>
+      <c r="R23" s="52"/>
+      <c r="S23" s="52"/>
+      <c r="T23" s="63"/>
     </row>
     <row r="24" spans="1:27" s="15" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
+      <c r="A24" s="41"/>
       <c r="B24" s="4" t="s">
         <v>49</v>
       </c>
@@ -2332,7 +2317,7 @@
       <c r="G24" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="50"/>
+      <c r="I24" s="72"/>
       <c r="J24" s="4" t="s">
         <v>54</v>
       </c>
@@ -2510,13 +2495,13 @@
       </c>
     </row>
     <row r="32" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="76" t="s">
+      <c r="A32" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="77"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="78"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="66"/>
       <c r="F32" s="23" t="s">
         <v>41</v>
       </c>
@@ -2532,163 +2517,163 @@
       <c r="J32" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="L32" s="79" t="s">
+      <c r="L32" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="M32" s="80"/>
-      <c r="N32" s="81"/>
+      <c r="M32" s="68"/>
+      <c r="N32" s="69"/>
       <c r="O32" s="25" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="72"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="75"/>
       <c r="F33" s="26"/>
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
       <c r="J33" s="26"/>
-      <c r="L33" s="70" t="s">
+      <c r="L33" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="M33" s="71"/>
-      <c r="N33" s="72"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
       <c r="O33" s="26"/>
     </row>
     <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="70" t="s">
+      <c r="A34" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="72"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="75"/>
       <c r="F34" s="26"/>
       <c r="G34" s="26"/>
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
-      <c r="L34" s="70" t="s">
+      <c r="L34" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="M34" s="71"/>
-      <c r="N34" s="72"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
       <c r="O34" s="26"/>
     </row>
     <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="70" t="s">
+      <c r="A35" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="72"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="75"/>
       <c r="F35" s="26"/>
       <c r="G35" s="26"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
-      <c r="L35" s="70" t="s">
+      <c r="L35" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="M35" s="71"/>
-      <c r="N35" s="72"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
       <c r="O35" s="26"/>
     </row>
     <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="70" t="s">
+      <c r="A36" s="73" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="72"/>
+      <c r="B36" s="74"/>
+      <c r="C36" s="74"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="75"/>
       <c r="F36" s="26"/>
       <c r="G36" s="26"/>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
       <c r="J36" s="26"/>
-      <c r="L36" s="70" t="s">
+      <c r="L36" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="M36" s="71"/>
-      <c r="N36" s="72"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
       <c r="O36" s="26"/>
     </row>
     <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="70" t="s">
+      <c r="A37" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="72"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="75"/>
       <c r="F37" s="26"/>
       <c r="G37" s="26"/>
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
       <c r="J37" s="26"/>
-      <c r="L37" s="70" t="s">
+      <c r="L37" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="M37" s="71"/>
-      <c r="N37" s="72"/>
+      <c r="M37" s="74"/>
+      <c r="N37" s="75"/>
       <c r="O37" s="26"/>
     </row>
     <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="70" t="s">
+      <c r="A38" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="72"/>
+      <c r="B38" s="74"/>
+      <c r="C38" s="74"/>
+      <c r="D38" s="74"/>
+      <c r="E38" s="75"/>
       <c r="F38" s="26"/>
       <c r="G38" s="26"/>
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
       <c r="J38" s="26"/>
-      <c r="L38" s="70" t="s">
+      <c r="L38" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="M38" s="71"/>
-      <c r="N38" s="72"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
       <c r="O38" s="26"/>
     </row>
     <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="72"/>
+      <c r="B39" s="74"/>
+      <c r="C39" s="74"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="75"/>
       <c r="F39" s="26"/>
       <c r="G39" s="26"/>
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
       <c r="J39" s="26"/>
-      <c r="L39" s="70" t="s">
+      <c r="L39" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="M39" s="71"/>
-      <c r="N39" s="72"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="75"/>
       <c r="O39" s="26"/>
     </row>
     <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="B40" s="71"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="72"/>
+      <c r="B40" s="74"/>
+      <c r="C40" s="74"/>
+      <c r="D40" s="74"/>
+      <c r="E40" s="75"/>
       <c r="F40" s="26"/>
       <c r="G40" s="26"/>
       <c r="H40" s="26"/>
@@ -2696,13 +2681,13 @@
       <c r="J40" s="26"/>
     </row>
     <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="70" t="s">
+      <c r="A41" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="72"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="74"/>
+      <c r="D41" s="74"/>
+      <c r="E41" s="75"/>
       <c r="F41" s="26"/>
       <c r="G41" s="26"/>
       <c r="H41" s="26"/>
@@ -2710,13 +2695,13 @@
       <c r="J41" s="26"/>
     </row>
     <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="70" t="s">
+      <c r="A42" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="72"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="75"/>
       <c r="F42" s="26"/>
       <c r="G42" s="26"/>
       <c r="H42" s="26"/>
@@ -2724,13 +2709,13 @@
       <c r="J42" s="26"/>
     </row>
     <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="70" t="s">
+      <c r="A43" s="73" t="s">
         <v>86</v>
       </c>
-      <c r="B43" s="71"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="72"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="74"/>
+      <c r="E43" s="75"/>
       <c r="F43" s="26"/>
       <c r="G43" s="26"/>
       <c r="H43" s="26"/>
@@ -2738,13 +2723,13 @@
       <c r="J43" s="26"/>
     </row>
     <row r="44" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="70" t="s">
+      <c r="A44" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="71"/>
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
-      <c r="E44" s="72"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="75"/>
       <c r="F44" s="26"/>
       <c r="G44" s="26"/>
       <c r="H44" s="26"/>
@@ -2752,13 +2737,13 @@
       <c r="J44" s="26"/>
     </row>
     <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="70" t="s">
+      <c r="A45" s="73" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="71"/>
-      <c r="C45" s="71"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="72"/>
+      <c r="B45" s="74"/>
+      <c r="C45" s="74"/>
+      <c r="D45" s="74"/>
+      <c r="E45" s="75"/>
       <c r="F45" s="26"/>
       <c r="G45" s="26"/>
       <c r="H45" s="26"/>
@@ -2766,13 +2751,13 @@
       <c r="J45" s="26"/>
     </row>
     <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="70" t="s">
+      <c r="A46" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="72"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="75"/>
       <c r="F46" s="26"/>
       <c r="G46" s="26"/>
       <c r="H46" s="26"/>
@@ -2780,13 +2765,13 @@
       <c r="J46" s="26"/>
     </row>
     <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="70" t="s">
+      <c r="A47" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
-      <c r="D47" s="71"/>
-      <c r="E47" s="72"/>
+      <c r="B47" s="74"/>
+      <c r="C47" s="74"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="75"/>
       <c r="F47" s="26"/>
       <c r="G47" s="26"/>
       <c r="H47" s="26"/>
@@ -2806,37 +2791,37 @@
       </c>
     </row>
     <row r="50" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="48" t="s">
+      <c r="A50" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="60" t="s">
+      <c r="B50" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="61"/>
-      <c r="D50" s="73"/>
-      <c r="E50" s="60" t="s">
+      <c r="C50" s="43"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="F50" s="61"/>
-      <c r="G50" s="73"/>
-      <c r="H50" s="51" t="s">
+      <c r="F50" s="43"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="I50" s="64"/>
-      <c r="J50" s="51" t="s">
+      <c r="I50" s="46"/>
+      <c r="J50" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="K50" s="54"/>
-      <c r="M50" s="48" t="s">
+      <c r="K50" s="62"/>
+      <c r="M50" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="N50" s="52" t="s">
+      <c r="N50" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="O50" s="52" t="s">
+      <c r="O50" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="P50" s="68" t="s">
+      <c r="P50" s="56" t="s">
         <v>97</v>
       </c>
       <c r="R50" s="27" t="s">
@@ -2847,31 +2832,31 @@
       <c r="U50" s="29"/>
     </row>
     <row r="51" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="49"/>
-      <c r="B51" s="63" t="s">
+      <c r="A51" s="71"/>
+      <c r="B51" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="63" t="s">
+      <c r="C51" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="63" t="s">
+      <c r="D51" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="E51" s="63" t="s">
+      <c r="E51" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="F51" s="56" t="s">
+      <c r="F51" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="G51" s="58"/>
-      <c r="H51" s="65"/>
-      <c r="I51" s="66"/>
-      <c r="J51" s="65"/>
-      <c r="K51" s="67"/>
-      <c r="M51" s="49"/>
-      <c r="N51" s="53"/>
-      <c r="O51" s="53"/>
-      <c r="P51" s="69"/>
+      <c r="G51" s="60"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="47"/>
+      <c r="K51" s="63"/>
+      <c r="M51" s="71"/>
+      <c r="N51" s="55"/>
+      <c r="O51" s="55"/>
+      <c r="P51" s="77"/>
       <c r="R51" s="30" t="s">
         <v>103</v>
       </c>
@@ -2880,11 +2865,11 @@
       <c r="U51" s="29"/>
     </row>
     <row r="52" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="50"/>
-      <c r="B52" s="53"/>
-      <c r="C52" s="53"/>
-      <c r="D52" s="53"/>
-      <c r="E52" s="53"/>
+      <c r="A52" s="72"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
       <c r="F52" s="4" t="s">
         <v>5</v>
       </c>
@@ -2903,10 +2888,10 @@
       <c r="K52" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="M52" s="50"/>
-      <c r="N52" s="53"/>
-      <c r="O52" s="53"/>
-      <c r="P52" s="69"/>
+      <c r="M52" s="72"/>
+      <c r="N52" s="55"/>
+      <c r="O52" s="55"/>
+      <c r="P52" s="77"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
@@ -3019,101 +3004,101 @@
       </c>
     </row>
     <row r="60" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B60" s="60" t="s">
+      <c r="B60" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="C60" s="61"/>
-      <c r="D60" s="61"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61"/>
-      <c r="J60" s="61"/>
-      <c r="K60" s="61"/>
-      <c r="L60" s="61"/>
-      <c r="M60" s="61"/>
-      <c r="N60" s="61"/>
-      <c r="O60" s="61"/>
-      <c r="P60" s="61"/>
-      <c r="Q60" s="61"/>
-      <c r="R60" s="61"/>
-      <c r="S60" s="61"/>
-      <c r="T60" s="61"/>
-      <c r="U60" s="61"/>
-      <c r="V60" s="62"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="43"/>
+      <c r="F60" s="43"/>
+      <c r="G60" s="43"/>
+      <c r="H60" s="43"/>
+      <c r="I60" s="43"/>
+      <c r="J60" s="43"/>
+      <c r="K60" s="43"/>
+      <c r="L60" s="43"/>
+      <c r="M60" s="43"/>
+      <c r="N60" s="43"/>
+      <c r="O60" s="43"/>
+      <c r="P60" s="43"/>
+      <c r="Q60" s="43"/>
+      <c r="R60" s="43"/>
+      <c r="S60" s="43"/>
+      <c r="T60" s="43"/>
+      <c r="U60" s="43"/>
+      <c r="V60" s="79"/>
     </row>
     <row r="61" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="49"/>
-      <c r="B61" s="56" t="s">
+      <c r="A61" s="71"/>
+      <c r="B61" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="58"/>
-      <c r="I61" s="56" t="s">
+      <c r="C61" s="59"/>
+      <c r="D61" s="59"/>
+      <c r="E61" s="59"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="59"/>
+      <c r="H61" s="60"/>
+      <c r="I61" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="J61" s="57"/>
-      <c r="K61" s="57"/>
-      <c r="L61" s="57"/>
-      <c r="M61" s="57"/>
-      <c r="N61" s="57"/>
-      <c r="O61" s="58"/>
-      <c r="P61" s="56" t="s">
+      <c r="J61" s="59"/>
+      <c r="K61" s="59"/>
+      <c r="L61" s="59"/>
+      <c r="M61" s="59"/>
+      <c r="N61" s="59"/>
+      <c r="O61" s="60"/>
+      <c r="P61" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="Q61" s="57"/>
-      <c r="R61" s="57"/>
-      <c r="S61" s="57"/>
-      <c r="T61" s="57"/>
-      <c r="U61" s="57"/>
-      <c r="V61" s="59"/>
+      <c r="Q61" s="59"/>
+      <c r="R61" s="59"/>
+      <c r="S61" s="59"/>
+      <c r="T61" s="59"/>
+      <c r="U61" s="59"/>
+      <c r="V61" s="78"/>
     </row>
     <row r="62" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="49"/>
-      <c r="B62" s="56" t="s">
+      <c r="A62" s="71"/>
+      <c r="B62" s="58" t="s">
         <v>112</v>
       </c>
-      <c r="C62" s="57"/>
-      <c r="D62" s="57"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="56" t="s">
+      <c r="C62" s="59"/>
+      <c r="D62" s="59"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="G62" s="57"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="56" t="s">
+      <c r="G62" s="59"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="58" t="s">
         <v>112</v>
       </c>
-      <c r="J62" s="57"/>
-      <c r="K62" s="57"/>
-      <c r="L62" s="58"/>
-      <c r="M62" s="56" t="s">
+      <c r="J62" s="59"/>
+      <c r="K62" s="59"/>
+      <c r="L62" s="60"/>
+      <c r="M62" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="N62" s="57"/>
-      <c r="O62" s="58"/>
-      <c r="P62" s="56" t="s">
+      <c r="N62" s="59"/>
+      <c r="O62" s="60"/>
+      <c r="P62" s="58" t="s">
         <v>112</v>
       </c>
-      <c r="Q62" s="57"/>
-      <c r="R62" s="57"/>
-      <c r="S62" s="58"/>
-      <c r="T62" s="57" t="s">
+      <c r="Q62" s="59"/>
+      <c r="R62" s="59"/>
+      <c r="S62" s="60"/>
+      <c r="T62" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="U62" s="57"/>
-      <c r="V62" s="59"/>
+      <c r="U62" s="59"/>
+      <c r="V62" s="78"/>
     </row>
     <row r="63" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="50"/>
+      <c r="A63" s="72"/>
       <c r="B63" s="4" t="s">
         <v>24</v>
       </c>
@@ -3309,17 +3294,17 @@
       <c r="V68" s="18"/>
     </row>
     <row r="71" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="48" t="s">
+      <c r="A71" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B71" s="60" t="s">
+      <c r="B71" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="C71" s="61"/>
-      <c r="D71" s="61"/>
-      <c r="E71" s="61"/>
-      <c r="F71" s="61"/>
-      <c r="G71" s="62"/>
+      <c r="C71" s="43"/>
+      <c r="D71" s="43"/>
+      <c r="E71" s="43"/>
+      <c r="F71" s="43"/>
+      <c r="G71" s="79"/>
       <c r="I71" s="32" t="s">
         <v>116</v>
       </c>
@@ -3330,17 +3315,17 @@
       <c r="N71" s="34"/>
     </row>
     <row r="72" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="49"/>
-      <c r="B72" s="56" t="s">
+      <c r="A72" s="71"/>
+      <c r="B72" s="58" t="s">
         <v>109</v>
       </c>
-      <c r="C72" s="58"/>
-      <c r="D72" s="56" t="s">
+      <c r="C72" s="60"/>
+      <c r="D72" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="E72" s="57"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="59"/>
+      <c r="E72" s="59"/>
+      <c r="F72" s="59"/>
+      <c r="G72" s="78"/>
       <c r="I72" s="35" t="s">
         <v>116</v>
       </c>
@@ -3351,49 +3336,49 @@
       <c r="N72" s="37"/>
     </row>
     <row r="73" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="49"/>
-      <c r="B73" s="40" t="s">
+      <c r="A73" s="71"/>
+      <c r="B73" s="80" t="s">
         <v>117</v>
       </c>
-      <c r="C73" s="40" t="s">
+      <c r="C73" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="D73" s="40" t="s">
+      <c r="D73" s="80" t="s">
         <v>119</v>
       </c>
-      <c r="E73" s="40" t="s">
+      <c r="E73" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="F73" s="40" t="s">
+      <c r="F73" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="G73" s="40" t="s">
+      <c r="G73" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="I73" s="42" t="s">
+      <c r="I73" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="J73" s="43"/>
-      <c r="K73" s="43"/>
-      <c r="L73" s="43"/>
-      <c r="M73" s="44"/>
+      <c r="J73" s="82"/>
+      <c r="K73" s="82"/>
+      <c r="L73" s="82"/>
+      <c r="M73" s="83"/>
       <c r="N73" s="29"/>
     </row>
     <row r="74" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="50"/>
-      <c r="B74" s="41"/>
-      <c r="C74" s="41"/>
-      <c r="D74" s="41"/>
-      <c r="E74" s="41"/>
-      <c r="F74" s="41"/>
-      <c r="G74" s="41"/>
-      <c r="I74" s="45" t="s">
+      <c r="A74" s="72"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="49"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="I74" s="84" t="s">
         <v>116</v>
       </c>
-      <c r="J74" s="46"/>
-      <c r="K74" s="46"/>
-      <c r="L74" s="46"/>
-      <c r="M74" s="47"/>
+      <c r="J74" s="85"/>
+      <c r="K74" s="85"/>
+      <c r="L74" s="85"/>
+      <c r="M74" s="86"/>
       <c r="N74" s="29"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
@@ -3457,30 +3442,30 @@
       </c>
     </row>
     <row r="82" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="48" t="s">
+      <c r="A82" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B82" s="51" t="s">
+      <c r="B82" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="C82" s="52" t="s">
+      <c r="C82" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="D82" s="54" t="s">
+      <c r="D82" s="62" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="49"/>
-      <c r="B83" s="41"/>
-      <c r="C83" s="53"/>
-      <c r="D83" s="55"/>
+      <c r="A83" s="71"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="55"/>
+      <c r="D83" s="87"/>
     </row>
     <row r="84" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="50"/>
-      <c r="B84" s="41"/>
-      <c r="C84" s="53"/>
-      <c r="D84" s="55"/>
+      <c r="A84" s="72"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="55"/>
+      <c r="D84" s="87"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
@@ -3524,65 +3509,14 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="A5:Y5"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="H13:I14"/>
-    <mergeCell ref="J13:K14"/>
-    <mergeCell ref="L13:M14"/>
-    <mergeCell ref="N13:P14"/>
-    <mergeCell ref="Q13:R14"/>
-    <mergeCell ref="S13:T14"/>
-    <mergeCell ref="U13:U15"/>
-    <mergeCell ref="V13:Z13"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:T23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="F22:G23"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="O50:O52"/>
-    <mergeCell ref="P50:P52"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="I62:L62"/>
-    <mergeCell ref="H50:I51"/>
-    <mergeCell ref="J50:K51"/>
-    <mergeCell ref="M50:M52"/>
-    <mergeCell ref="N50:N52"/>
-    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="I74:M74"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C82:C84"/>
+    <mergeCell ref="D82:D84"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
     <mergeCell ref="P62:S62"/>
     <mergeCell ref="T62:V62"/>
     <mergeCell ref="A71:A74"/>
@@ -3599,22 +3533,73 @@
     <mergeCell ref="P61:V61"/>
     <mergeCell ref="B62:E62"/>
     <mergeCell ref="I73:M73"/>
-    <mergeCell ref="I74:M74"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C82:C84"/>
-    <mergeCell ref="D82:D84"/>
+    <mergeCell ref="I62:L62"/>
+    <mergeCell ref="H50:I51"/>
+    <mergeCell ref="J50:K51"/>
+    <mergeCell ref="M50:M52"/>
+    <mergeCell ref="N50:N52"/>
+    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="O50:O52"/>
+    <mergeCell ref="P50:P52"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:T23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="A5:Y5"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="H13:I14"/>
+    <mergeCell ref="J13:K14"/>
+    <mergeCell ref="L13:M14"/>
+    <mergeCell ref="N13:P14"/>
+    <mergeCell ref="Q13:R14"/>
+    <mergeCell ref="S13:T14"/>
+    <mergeCell ref="U13:U15"/>
+    <mergeCell ref="V13:Z13"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/uploads/Reporte_Actividades_Materno.xlsx
+++ b/uploads/Reporte_Actividades_Materno.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jhon\Esni app\materno\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jhon\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A3D0D8-0789-4F95-A19B-2BC30536DDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDEEB31-E741-4E2D-8D22-9A50D2D08476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,7 +426,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,6 +522,61 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1284,7 +1339,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1350,31 +1405,16 @@
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="4" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1395,161 +1435,332 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="4" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="4" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1832,6 +2043,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A5:AA89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1839,50 +2053,50 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="48"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
     </row>
     <row r="8" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="89"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="M8" s="2"/>
@@ -1910,84 +2124,84 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="45" t="s">
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="46"/>
-      <c r="J13" s="45" t="s">
+      <c r="I13" s="74"/>
+      <c r="J13" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="K13" s="46"/>
-      <c r="L13" s="45" t="s">
+      <c r="K13" s="74"/>
+      <c r="L13" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="46"/>
-      <c r="N13" s="49" t="s">
+      <c r="M13" s="74"/>
+      <c r="N13" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="O13" s="50"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="53" t="s">
+      <c r="O13" s="76"/>
+      <c r="P13" s="77"/>
+      <c r="Q13" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="R13" s="54"/>
-      <c r="S13" s="53" t="s">
+      <c r="R13" s="79"/>
+      <c r="S13" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="T13" s="46"/>
-      <c r="U13" s="55" t="s">
+      <c r="T13" s="74"/>
+      <c r="U13" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="V13" s="47" t="s">
+      <c r="V13" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="W13" s="52"/>
-      <c r="X13" s="52"/>
-      <c r="Y13" s="52"/>
-      <c r="Z13" s="48"/>
-      <c r="AA13" s="56" t="s">
+      <c r="W13" s="90"/>
+      <c r="X13" s="90"/>
+      <c r="Y13" s="90"/>
+      <c r="Z13" s="91"/>
+      <c r="AA13" s="42" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="40"/>
-      <c r="B14" s="58" t="s">
+      <c r="A14" s="52"/>
+      <c r="B14" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="61" t="s">
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="61" t="s">
+      <c r="G14" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="47"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="48"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="52"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="48"/>
-      <c r="U14" s="55"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="80"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="81"/>
+      <c r="U14" s="38"/>
       <c r="V14" s="7" t="s">
         <v>18</v>
       </c>
@@ -2003,24 +2217,24 @@
       <c r="Z14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AA14" s="57"/>
+      <c r="AA14" s="47"/>
     </row>
     <row r="15" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41"/>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="53"/>
+      <c r="B15" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
       <c r="H15" s="6" t="s">
         <v>27</v>
       </c>
@@ -2060,7 +2274,7 @@
       <c r="T15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="U15" s="55"/>
+      <c r="U15" s="38"/>
       <c r="V15" s="6" t="s">
         <v>36</v>
       </c>
@@ -2236,73 +2450,73 @@
       <c r="AA20" s="14"/>
     </row>
     <row r="22" spans="1:27" s="15" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="45" t="s">
+      <c r="C22" s="95"/>
+      <c r="D22" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="46"/>
-      <c r="F22" s="45" t="s">
+      <c r="E22" s="95"/>
+      <c r="F22" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="62"/>
-      <c r="I22" s="70" t="s">
+      <c r="G22" s="96"/>
+      <c r="I22" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="J22" s="42" t="s">
+      <c r="J22" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="45" t="s">
+      <c r="K22" s="55"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="55"/>
+      <c r="P22" s="56"/>
+      <c r="Q22" s="83" t="s">
         <v>45</v>
       </c>
-      <c r="R22" s="54"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="62"/>
+      <c r="R22" s="85"/>
+      <c r="S22" s="85"/>
+      <c r="T22" s="92"/>
     </row>
     <row r="23" spans="1:27" s="15" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="40"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="63"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="58" t="s">
+      <c r="A23" s="52"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="97"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="58" t="s">
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="O23" s="60"/>
-      <c r="P23" s="7" t="s">
+      <c r="O23" s="41"/>
+      <c r="P23" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="52"/>
-      <c r="S23" s="52"/>
-      <c r="T23" s="63"/>
+      <c r="Q23" s="86"/>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="93"/>
     </row>
     <row r="24" spans="1:27" s="15" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="41"/>
-      <c r="B24" s="4" t="s">
+      <c r="A24" s="53"/>
+      <c r="B24" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="98" t="s">
         <v>50</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -2317,7 +2531,7 @@
       <c r="G24" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="72"/>
+      <c r="I24" s="101"/>
       <c r="J24" s="4" t="s">
         <v>54</v>
       </c>
@@ -2495,288 +2709,288 @@
       </c>
     </row>
     <row r="32" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="64" t="s">
+      <c r="A32" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="65"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="65"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="23" t="s">
+      <c r="B32" s="104"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="H32" s="106" t="s">
         <v>38</v>
       </c>
-      <c r="I32" s="23" t="s">
+      <c r="I32" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="J32" s="24" t="s">
+      <c r="J32" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="L32" s="67" t="s">
+      <c r="L32" s="108" t="s">
         <v>68</v>
       </c>
-      <c r="M32" s="68"/>
-      <c r="N32" s="69"/>
-      <c r="O32" s="25" t="s">
+      <c r="M32" s="109"/>
+      <c r="N32" s="110"/>
+      <c r="O32" s="111" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="73" t="s">
+      <c r="A33" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="74"/>
-      <c r="C33" s="74"/>
-      <c r="D33" s="74"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="L33" s="73" t="s">
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="L33" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="M33" s="74"/>
-      <c r="N33" s="75"/>
-      <c r="O33" s="26"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="23"/>
     </row>
     <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="73" t="s">
+      <c r="A34" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="74"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="L34" s="73" t="s">
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+      <c r="L34" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="M34" s="74"/>
-      <c r="N34" s="75"/>
-      <c r="O34" s="26"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="45"/>
+      <c r="O34" s="23"/>
     </row>
     <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="74"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="L35" s="73" t="s">
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="L35" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="M35" s="74"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="26"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="45"/>
+      <c r="O35" s="23"/>
     </row>
     <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="73" t="s">
+      <c r="A36" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="74"/>
-      <c r="C36" s="74"/>
-      <c r="D36" s="74"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="L36" s="73" t="s">
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+      <c r="L36" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="M36" s="74"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="26"/>
+      <c r="M36" s="44"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="23"/>
     </row>
     <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="74"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="75"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="L37" s="73" t="s">
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="23"/>
+      <c r="L37" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="M37" s="74"/>
-      <c r="N37" s="75"/>
-      <c r="O37" s="26"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="45"/>
+      <c r="O37" s="23"/>
     </row>
     <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="73" t="s">
+      <c r="A38" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="74"/>
-      <c r="C38" s="74"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="L38" s="73" t="s">
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="L38" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="M38" s="74"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="26"/>
+      <c r="M38" s="44"/>
+      <c r="N38" s="45"/>
+      <c r="O38" s="23"/>
     </row>
     <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="74"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="L39" s="73" t="s">
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+      <c r="L39" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="M39" s="74"/>
-      <c r="N39" s="75"/>
-      <c r="O39" s="26"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="45"/>
+      <c r="O39" s="23"/>
     </row>
     <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="B40" s="74"/>
-      <c r="C40" s="74"/>
-      <c r="D40" s="74"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
     </row>
     <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="73" t="s">
+      <c r="A41" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="B41" s="74"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
     </row>
     <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
     </row>
     <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="B43" s="74"/>
-      <c r="C43" s="74"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
     </row>
     <row r="44" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="74"/>
-      <c r="C44" s="74"/>
-      <c r="D44" s="74"/>
-      <c r="E44" s="75"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
     </row>
     <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="73" t="s">
+      <c r="A45" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="74"/>
-      <c r="C45" s="74"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="75"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="23"/>
     </row>
     <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="73" t="s">
+      <c r="A46" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="B46" s="74"/>
-      <c r="C46" s="74"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="75"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="23"/>
     </row>
     <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="74"/>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="23"/>
+      <c r="J47" s="23"/>
     </row>
     <row r="48" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
@@ -2791,107 +3005,107 @@
       </c>
     </row>
     <row r="50" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="70" t="s">
+      <c r="A50" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="42" t="s">
+      <c r="B50" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="42" t="s">
+      <c r="C50" s="55"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="F50" s="43"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="45" t="s">
+      <c r="F50" s="55"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="I50" s="46"/>
-      <c r="J50" s="45" t="s">
+      <c r="I50" s="84"/>
+      <c r="J50" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="K50" s="62"/>
-      <c r="M50" s="70" t="s">
+      <c r="K50" s="92"/>
+      <c r="M50" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="N50" s="76" t="s">
+      <c r="N50" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="O50" s="76" t="s">
+      <c r="O50" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="P50" s="56" t="s">
+      <c r="P50" s="120" t="s">
         <v>97</v>
       </c>
-      <c r="R50" s="27" t="s">
+      <c r="R50" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="S50" s="28"/>
-      <c r="T50" s="28"/>
-      <c r="U50" s="29"/>
+      <c r="S50" s="124"/>
+      <c r="T50" s="24"/>
+      <c r="U50" s="25"/>
     </row>
     <row r="51" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="71"/>
-      <c r="B51" s="61" t="s">
+      <c r="A51" s="100"/>
+      <c r="B51" s="115" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C51" s="115" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="61" t="s">
+      <c r="D51" s="115" t="s">
         <v>101</v>
       </c>
-      <c r="E51" s="61" t="s">
+      <c r="E51" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="F51" s="58" t="s">
+      <c r="F51" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="G51" s="60"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="47"/>
-      <c r="K51" s="63"/>
-      <c r="M51" s="71"/>
-      <c r="N51" s="55"/>
-      <c r="O51" s="55"/>
-      <c r="P51" s="77"/>
-      <c r="R51" s="30" t="s">
+      <c r="G51" s="67"/>
+      <c r="H51" s="86"/>
+      <c r="I51" s="87"/>
+      <c r="J51" s="86"/>
+      <c r="K51" s="93"/>
+      <c r="M51" s="113"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="121"/>
+      <c r="P51" s="122"/>
+      <c r="R51" s="125" t="s">
         <v>103</v>
       </c>
-      <c r="S51" s="31"/>
-      <c r="T51" s="31"/>
-      <c r="U51" s="29"/>
+      <c r="S51" s="126"/>
+      <c r="T51" s="26"/>
+      <c r="U51" s="25"/>
     </row>
     <row r="52" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="72"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="4" t="s">
+      <c r="A52" s="101"/>
+      <c r="B52" s="116"/>
+      <c r="C52" s="116"/>
+      <c r="D52" s="116"/>
+      <c r="E52" s="116"/>
+      <c r="F52" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H52" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="I52" s="4" t="s">
+      <c r="I52" s="117" t="s">
         <v>100</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="K52" s="16" t="s">
+      <c r="K52" s="118" t="s">
         <v>106</v>
       </c>
-      <c r="M52" s="72"/>
-      <c r="N52" s="55"/>
-      <c r="O52" s="55"/>
-      <c r="P52" s="77"/>
+      <c r="M52" s="114"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="122"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
@@ -3004,162 +3218,162 @@
       </c>
     </row>
     <row r="60" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="70" t="s">
+      <c r="A60" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="B60" s="42" t="s">
+      <c r="B60" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="C60" s="43"/>
-      <c r="D60" s="43"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="43"/>
-      <c r="H60" s="43"/>
-      <c r="I60" s="43"/>
-      <c r="J60" s="43"/>
-      <c r="K60" s="43"/>
-      <c r="L60" s="43"/>
-      <c r="M60" s="43"/>
-      <c r="N60" s="43"/>
-      <c r="O60" s="43"/>
-      <c r="P60" s="43"/>
-      <c r="Q60" s="43"/>
-      <c r="R60" s="43"/>
-      <c r="S60" s="43"/>
-      <c r="T60" s="43"/>
-      <c r="U60" s="43"/>
-      <c r="V60" s="79"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+      <c r="H60" s="58"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="58"/>
+      <c r="K60" s="58"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
+      <c r="P60" s="58"/>
+      <c r="Q60" s="58"/>
+      <c r="R60" s="58"/>
+      <c r="S60" s="58"/>
+      <c r="T60" s="58"/>
+      <c r="U60" s="58"/>
+      <c r="V60" s="127"/>
     </row>
     <row r="61" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="71"/>
-      <c r="B61" s="58" t="s">
+      <c r="A61" s="100"/>
+      <c r="B61" s="65" t="s">
         <v>109</v>
       </c>
-      <c r="C61" s="59"/>
-      <c r="D61" s="59"/>
-      <c r="E61" s="59"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="59"/>
-      <c r="H61" s="60"/>
-      <c r="I61" s="58" t="s">
+      <c r="C61" s="66"/>
+      <c r="D61" s="66"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="66"/>
+      <c r="G61" s="66"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="J61" s="59"/>
-      <c r="K61" s="59"/>
-      <c r="L61" s="59"/>
-      <c r="M61" s="59"/>
-      <c r="N61" s="59"/>
-      <c r="O61" s="60"/>
-      <c r="P61" s="58" t="s">
+      <c r="J61" s="66"/>
+      <c r="K61" s="66"/>
+      <c r="L61" s="66"/>
+      <c r="M61" s="66"/>
+      <c r="N61" s="66"/>
+      <c r="O61" s="67"/>
+      <c r="P61" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="Q61" s="59"/>
-      <c r="R61" s="59"/>
-      <c r="S61" s="59"/>
-      <c r="T61" s="59"/>
-      <c r="U61" s="59"/>
-      <c r="V61" s="78"/>
+      <c r="Q61" s="66"/>
+      <c r="R61" s="66"/>
+      <c r="S61" s="66"/>
+      <c r="T61" s="66"/>
+      <c r="U61" s="66"/>
+      <c r="V61" s="129"/>
     </row>
     <row r="62" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="71"/>
-      <c r="B62" s="58" t="s">
+      <c r="A62" s="100"/>
+      <c r="B62" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="C62" s="59"/>
-      <c r="D62" s="59"/>
-      <c r="E62" s="60"/>
-      <c r="F62" s="58" t="s">
+      <c r="C62" s="66"/>
+      <c r="D62" s="66"/>
+      <c r="E62" s="67"/>
+      <c r="F62" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="G62" s="59"/>
-      <c r="H62" s="60"/>
-      <c r="I62" s="58" t="s">
+      <c r="G62" s="66"/>
+      <c r="H62" s="67"/>
+      <c r="I62" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="J62" s="59"/>
-      <c r="K62" s="59"/>
-      <c r="L62" s="60"/>
-      <c r="M62" s="58" t="s">
+      <c r="J62" s="66"/>
+      <c r="K62" s="66"/>
+      <c r="L62" s="67"/>
+      <c r="M62" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="N62" s="59"/>
-      <c r="O62" s="60"/>
-      <c r="P62" s="58" t="s">
+      <c r="N62" s="66"/>
+      <c r="O62" s="67"/>
+      <c r="P62" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="Q62" s="59"/>
-      <c r="R62" s="59"/>
-      <c r="S62" s="60"/>
-      <c r="T62" s="59" t="s">
+      <c r="Q62" s="66"/>
+      <c r="R62" s="66"/>
+      <c r="S62" s="67"/>
+      <c r="T62" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="U62" s="59"/>
-      <c r="V62" s="78"/>
+      <c r="U62" s="66"/>
+      <c r="V62" s="129"/>
     </row>
     <row r="63" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
-      <c r="B63" s="4" t="s">
+      <c r="A63" s="101"/>
+      <c r="B63" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="117" t="s">
         <v>114</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G63" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="H63" s="4" t="s">
+      <c r="H63" s="117" t="s">
         <v>114</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="I63" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="J63" s="4" t="s">
+      <c r="J63" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K63" s="4" t="s">
+      <c r="K63" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="L63" s="4" t="s">
+      <c r="L63" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="M63" s="4" t="s">
+      <c r="M63" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="N63" s="4" t="s">
+      <c r="N63" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="O63" s="4" t="s">
+      <c r="O63" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="P63" s="4" t="s">
+      <c r="P63" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="Q63" s="4" t="s">
+      <c r="Q63" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="R63" s="4" t="s">
+      <c r="R63" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="S63" s="4" t="s">
+      <c r="S63" s="117" t="s">
         <v>114</v>
       </c>
-      <c r="T63" s="4" t="s">
+      <c r="T63" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="U63" s="4" t="s">
+      <c r="U63" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="V63" s="9" t="s">
+      <c r="V63" s="130" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3294,92 +3508,92 @@
       <c r="V68" s="18"/>
     </row>
     <row r="71" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="70" t="s">
+      <c r="A71" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="B71" s="42" t="s">
+      <c r="B71" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="C71" s="43"/>
-      <c r="D71" s="43"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="79"/>
-      <c r="I71" s="32" t="s">
+      <c r="C71" s="58"/>
+      <c r="D71" s="58"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="58"/>
+      <c r="G71" s="127"/>
+      <c r="I71" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="J71" s="33"/>
-      <c r="K71" s="33"/>
-      <c r="L71" s="33"/>
-      <c r="M71" s="33"/>
-      <c r="N71" s="34"/>
+      <c r="J71" s="28"/>
+      <c r="K71" s="28"/>
+      <c r="L71" s="28"/>
+      <c r="M71" s="28"/>
+      <c r="N71" s="29"/>
     </row>
     <row r="72" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="71"/>
-      <c r="B72" s="58" t="s">
+      <c r="A72" s="100"/>
+      <c r="B72" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="C72" s="60"/>
-      <c r="D72" s="58" t="s">
+      <c r="C72" s="64"/>
+      <c r="D72" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="E72" s="59"/>
-      <c r="F72" s="59"/>
-      <c r="G72" s="78"/>
-      <c r="I72" s="35" t="s">
+      <c r="E72" s="63"/>
+      <c r="F72" s="63"/>
+      <c r="G72" s="128"/>
+      <c r="I72" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="J72" s="36"/>
-      <c r="K72" s="36"/>
-      <c r="L72" s="36"/>
-      <c r="M72" s="36"/>
-      <c r="N72" s="37"/>
+      <c r="J72" s="31"/>
+      <c r="K72" s="31"/>
+      <c r="L72" s="31"/>
+      <c r="M72" s="31"/>
+      <c r="N72" s="32"/>
     </row>
     <row r="73" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="71"/>
-      <c r="B73" s="80" t="s">
+      <c r="A73" s="100"/>
+      <c r="B73" s="131" t="s">
         <v>117</v>
       </c>
-      <c r="C73" s="80" t="s">
+      <c r="C73" s="131" t="s">
         <v>118</v>
       </c>
-      <c r="D73" s="80" t="s">
+      <c r="D73" s="131" t="s">
         <v>119</v>
       </c>
-      <c r="E73" s="80" t="s">
+      <c r="E73" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="F73" s="80" t="s">
+      <c r="F73" s="131" t="s">
         <v>120</v>
       </c>
-      <c r="G73" s="80" t="s">
+      <c r="G73" s="131" t="s">
         <v>121</v>
       </c>
-      <c r="I73" s="81" t="s">
+      <c r="I73" s="132" t="s">
         <v>116</v>
       </c>
-      <c r="J73" s="82"/>
-      <c r="K73" s="82"/>
-      <c r="L73" s="82"/>
-      <c r="M73" s="83"/>
-      <c r="N73" s="29"/>
+      <c r="J73" s="133"/>
+      <c r="K73" s="133"/>
+      <c r="L73" s="133"/>
+      <c r="M73" s="134"/>
+      <c r="N73" s="25"/>
     </row>
     <row r="74" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="49"/>
-      <c r="D74" s="49"/>
-      <c r="E74" s="49"/>
-      <c r="F74" s="49"/>
-      <c r="G74" s="49"/>
-      <c r="I74" s="84" t="s">
+      <c r="A74" s="101"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="72"/>
+      <c r="D74" s="72"/>
+      <c r="E74" s="72"/>
+      <c r="F74" s="72"/>
+      <c r="G74" s="72"/>
+      <c r="I74" s="135" t="s">
         <v>116</v>
       </c>
-      <c r="J74" s="85"/>
-      <c r="K74" s="85"/>
-      <c r="L74" s="85"/>
-      <c r="M74" s="86"/>
-      <c r="N74" s="29"/>
+      <c r="J74" s="136"/>
+      <c r="K74" s="136"/>
+      <c r="L74" s="136"/>
+      <c r="M74" s="137"/>
+      <c r="N74" s="25"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
@@ -3442,30 +3656,30 @@
       </c>
     </row>
     <row r="82" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="70" t="s">
+      <c r="A82" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B82" s="45" t="s">
+      <c r="B82" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="C82" s="76" t="s">
+      <c r="C82" s="138" t="s">
         <v>124</v>
       </c>
-      <c r="D82" s="62" t="s">
+      <c r="D82" s="140" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="71"/>
-      <c r="B83" s="49"/>
-      <c r="C83" s="55"/>
-      <c r="D83" s="87"/>
+      <c r="A83" s="34"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="139"/>
+      <c r="D83" s="141"/>
     </row>
     <row r="84" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
-      <c r="B84" s="49"/>
-      <c r="C84" s="55"/>
-      <c r="D84" s="87"/>
+      <c r="A84" s="35"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="139"/>
+      <c r="D84" s="141"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
@@ -3509,14 +3723,73 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="I74:M74"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C82:C84"/>
-    <mergeCell ref="D82:D84"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="A5:Y5"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="H13:I14"/>
+    <mergeCell ref="J13:K14"/>
+    <mergeCell ref="L13:M14"/>
+    <mergeCell ref="N13:P14"/>
+    <mergeCell ref="Q13:R14"/>
+    <mergeCell ref="S13:T14"/>
+    <mergeCell ref="U13:U15"/>
+    <mergeCell ref="V13:Z13"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:T23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="P50:P52"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="I62:L62"/>
+    <mergeCell ref="H50:I51"/>
+    <mergeCell ref="J50:K51"/>
+    <mergeCell ref="M50:M52"/>
+    <mergeCell ref="N50:N52"/>
+    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="O50:O52"/>
     <mergeCell ref="P62:S62"/>
     <mergeCell ref="T62:V62"/>
     <mergeCell ref="A71:A74"/>
@@ -3533,74 +3806,19 @@
     <mergeCell ref="P61:V61"/>
     <mergeCell ref="B62:E62"/>
     <mergeCell ref="I73:M73"/>
-    <mergeCell ref="I62:L62"/>
-    <mergeCell ref="H50:I51"/>
-    <mergeCell ref="J50:K51"/>
-    <mergeCell ref="M50:M52"/>
-    <mergeCell ref="N50:N52"/>
-    <mergeCell ref="M62:O62"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="O50:O52"/>
-    <mergeCell ref="P50:P52"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="F22:G23"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:T23"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="A5:Y5"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="H13:I14"/>
-    <mergeCell ref="J13:K14"/>
-    <mergeCell ref="L13:M14"/>
-    <mergeCell ref="N13:P14"/>
-    <mergeCell ref="Q13:R14"/>
-    <mergeCell ref="S13:T14"/>
-    <mergeCell ref="U13:U15"/>
-    <mergeCell ref="V13:Z13"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="I74:M74"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C82:C84"/>
+    <mergeCell ref="D82:D84"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="G73:G74"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.11811023622047245" right="0" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="50" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="58" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>